--- a/artfynd/A 38915-2023 artfynd.xlsx
+++ b/artfynd/A 38915-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129612653</v>
       </c>
       <c r="B2" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>129612787</v>
       </c>
       <c r="B3" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>129612711</v>
       </c>
       <c r="B4" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>129612834</v>
       </c>
       <c r="B5" t="n">
-        <v>97601</v>
+        <v>97630</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         <v>129612293</v>
       </c>
       <c r="B6" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 38915-2023 artfynd.xlsx
+++ b/artfynd/A 38915-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129612653</v>
       </c>
       <c r="B2" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>129612787</v>
       </c>
       <c r="B3" t="n">
-        <v>57727</v>
+        <v>57732</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>129612711</v>
       </c>
       <c r="B4" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>129612834</v>
       </c>
       <c r="B5" t="n">
-        <v>97630</v>
+        <v>97642</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         <v>129612293</v>
       </c>
       <c r="B6" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 38915-2023 artfynd.xlsx
+++ b/artfynd/A 38915-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129612653</v>
       </c>
       <c r="B2" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>129612787</v>
       </c>
       <c r="B3" t="n">
-        <v>57732</v>
+        <v>57733</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>129612711</v>
       </c>
       <c r="B4" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>129612834</v>
       </c>
       <c r="B5" t="n">
-        <v>97642</v>
+        <v>97643</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         <v>129612293</v>
       </c>
       <c r="B6" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 38915-2023 artfynd.xlsx
+++ b/artfynd/A 38915-2023 artfynd.xlsx
@@ -1029,7 +1029,7 @@
         <v>129612834</v>
       </c>
       <c r="B5" t="n">
-        <v>97643</v>
+        <v>97648</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 38915-2023 artfynd.xlsx
+++ b/artfynd/A 38915-2023 artfynd.xlsx
@@ -1029,7 +1029,7 @@
         <v>129612834</v>
       </c>
       <c r="B5" t="n">
-        <v>97648</v>
+        <v>97652</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 38915-2023 artfynd.xlsx
+++ b/artfynd/A 38915-2023 artfynd.xlsx
@@ -1029,7 +1029,7 @@
         <v>129612834</v>
       </c>
       <c r="B5" t="n">
-        <v>97652</v>
+        <v>97654</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 38915-2023 artfynd.xlsx
+++ b/artfynd/A 38915-2023 artfynd.xlsx
@@ -1029,7 +1029,7 @@
         <v>129612834</v>
       </c>
       <c r="B5" t="n">
-        <v>97654</v>
+        <v>97664</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 38915-2023 artfynd.xlsx
+++ b/artfynd/A 38915-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129612653</v>
       </c>
       <c r="B2" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>129612787</v>
       </c>
       <c r="B3" t="n">
-        <v>57733</v>
+        <v>57734</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>129612711</v>
       </c>
       <c r="B4" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>129612834</v>
       </c>
       <c r="B5" t="n">
-        <v>97664</v>
+        <v>97668</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         <v>129612293</v>
       </c>
       <c r="B6" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 38915-2023 artfynd.xlsx
+++ b/artfynd/A 38915-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129612653</v>
       </c>
       <c r="B2" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>129612787</v>
       </c>
       <c r="B3" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>129612711</v>
       </c>
       <c r="B4" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>129612834</v>
       </c>
       <c r="B5" t="n">
-        <v>97668</v>
+        <v>97671</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         <v>129612293</v>
       </c>
       <c r="B6" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 38915-2023 artfynd.xlsx
+++ b/artfynd/A 38915-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,27 +675,27 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129612653</v>
+        <v>129298134</v>
       </c>
       <c r="B2" t="n">
-        <v>57740</v>
+        <v>56925</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>100045</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Sångsvan</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cygnus cygnus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -706,19 +706,19 @@
       <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>sträckande NO</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Skogskärr, Skogskärr, Nrk</t>
+          <t>Degerfors, Degerfors, Nrk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>467732</v>
+        <v>467799</v>
       </c>
       <c r="R2" t="n">
-        <v>6545006</v>
+        <v>6545206</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -745,27 +745,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
+          <t>2025-03-19</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>20:48</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
+          <t>2025-03-19</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:50</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Färska ringhack med rinnande kåda på gran i kanten mot ungskogen och i avverkningsanmälan. Märkt med gult litet band på gren.</t>
+          <t>20:48</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,12 +775,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Therese Steiner</t>
+          <t>David Tverling</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Therese Steiner</t>
+          <t>David Tverling</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -795,11 +790,11 @@
         <v>129612787</v>
       </c>
       <c r="B3" t="n">
-        <v>57737</v>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -909,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129612711</v>
+        <v>129612293</v>
       </c>
       <c r="B4" t="n">
-        <v>57740</v>
+        <v>57953</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -940,7 +935,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -949,10 +944,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>467732</v>
+        <v>467735</v>
       </c>
       <c r="R4" t="n">
-        <v>6545003</v>
+        <v>6545030</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -984,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,12 +989,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Äldre ringhack på gran i kanten mot ungskogen och i avverkningsanmälan. En bit ifrån gran med färska ringhack och märkt med gult litet band på gren. 2 träd totalt just här.</t>
+          <t>Färska ringhack med rinnande kåda på gran i kanten mot ungskogen och i avverkningsanmälan. Märkt med gult litet band på gren.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,45 +1021,50 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129612834</v>
+        <v>129612562</v>
       </c>
       <c r="B5" t="n">
-        <v>97671</v>
+        <v>57953</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221946</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>västanbäck sv, västanbäck sv, Nrk</t>
+          <t>Skogskärr, Skogskärr, Nrk</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>467799</v>
+        <v>467730</v>
       </c>
       <c r="R5" t="n">
-        <v>6545158</v>
+        <v>6545031</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1096,7 +1096,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1106,7 +1106,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:38</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran i kanten mot ungskogen och i avverkningsanmälan. Bredvid träd med färska och märkt med gult band.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1133,10 +1138,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129612293</v>
+        <v>129612620</v>
       </c>
       <c r="B6" t="n">
-        <v>57740</v>
+        <v>57953</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1173,10 +1178,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>467735</v>
+        <v>467730</v>
       </c>
       <c r="R6" t="n">
-        <v>6545030</v>
+        <v>6545027</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1208,7 +1213,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1218,12 +1223,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Färska ringhack med rinnande kåda på gran i kanten mot ungskogen och i avverkningsanmälan. Märkt med gult litet band på gren.</t>
+          <t>Färska ringhack med rinnande kåda på gran i kanten mot ungskogen och i avverkningsanmälan. Totalt 3 granar i denna grupp som har ringhack på sig.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1247,6 +1252,464 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>129612653</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Skogskärr, Skogskärr, Nrk</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>467732</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6545006</v>
+      </c>
+      <c r="S7" t="n">
+        <v>20</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Färska ringhack med rinnande kåda på gran i kanten mot ungskogen och i avverkningsanmälan. Märkt med gult litet band på gren.</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>129612711</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Skogskärr, Skogskärr, Nrk</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>467732</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6545003</v>
+      </c>
+      <c r="S8" t="n">
+        <v>20</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>11:51</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>11:51</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran i kanten mot ungskogen och i avverkningsanmälan. En bit ifrån gran med färska ringhack och märkt med gult litet band på gren. 2 träd totalt just här.</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>129612733</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Skogskärr, Skogskärr, Nrk</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>467724</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6544994</v>
+      </c>
+      <c r="S9" t="n">
+        <v>20</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran i kanten mot ungskogen och i avverkningsanmälan. Märkt med gult litet band på gren.</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>129612834</v>
+      </c>
+      <c r="B10" t="n">
+        <v>97986</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>västanbäck sv, västanbäck sv, Nrk</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>467799</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6545158</v>
+      </c>
+      <c r="S10" t="n">
+        <v>20</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>11:31</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>11:31</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 38915-2023 artfynd.xlsx
+++ b/artfynd/A 38915-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -784,6 +789,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129298134</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -901,6 +911,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129612787</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1018,6 +1033,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129612293</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1135,6 +1155,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129612562</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1252,6 +1277,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129612620</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1369,6 +1399,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129612653</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1486,6 +1521,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129612711</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1603,6 +1643,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129612733</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1710,8 +1755,24 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129612834</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>